--- a/layout/Layout_Garantias_V2_FILE_GARANTIAS_II.xlsx
+++ b/layout/Layout_Garantias_V2_FILE_GARANTIAS_II.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F697350-5581-4C60-AA08-3D30C3A9220F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D127AE-494B-454F-BF88-D2D3881D2B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50" yWindow="5510" windowWidth="20260" windowHeight="15950" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INDEX" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="69">
   <si>
     <t>Layout</t>
   </si>
@@ -87,9 +87,6 @@
     <t>Catalogo</t>
   </si>
   <si>
-    <t>Comentario BW</t>
-  </si>
-  <si>
     <t>OFICINA</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
     <t xml:space="preserve">No puede ser Vacio. </t>
   </si>
   <si>
-    <t>ANEXO A</t>
-  </si>
-  <si>
     <t>ID_GAR</t>
   </si>
   <si>
@@ -135,18 +129,12 @@
     <t>TIPO DE ACTIVO EN GARANTÍA</t>
   </si>
   <si>
-    <t>ANEXO AD</t>
-  </si>
-  <si>
     <t>CVE_TIT</t>
   </si>
   <si>
     <t>CLAVE DEL VALOR (TITULO DE DEUDA O ACCIÓN) EN GARANTÍA</t>
   </si>
   <si>
-    <t>ANEXO AF</t>
-  </si>
-  <si>
     <t>AFORO</t>
   </si>
   <si>
@@ -171,9 +159,6 @@
     <t>MONEDA DEL ACTIVO EN GARANTÍA</t>
   </si>
   <si>
-    <t>ANEXO E</t>
-  </si>
-  <si>
     <t>FECHAINFO</t>
   </si>
   <si>
@@ -193,9 +178,6 @@
   </si>
   <si>
     <t>CONTRAPARTE DEL CONTRATO DE GARANTÍA</t>
-  </si>
-  <si>
-    <t>ANEXO B</t>
   </si>
   <si>
     <t>POS_GTA</t>
@@ -221,9 +203,6 @@
     <t>GARANTE DEL CONTRATO DE GARANTÍA</t>
   </si>
   <si>
-    <t>ANEXO AG</t>
-  </si>
-  <si>
     <t xml:space="preserve">En caso que un activo individual del contrato de garantía a reportar, sea una garantía personal (avales, cartas de crédito, líneas de crédito, seguros de crédito, etc., pero excluyendo a los derivados de crédito), deberá anotarse la clave que corresponda al emisor o garante del activo en garantía de que se trate, conforme al “Catálogo de Garante del Contrato de Garantía”, a que se refiere el Anexo AG.
 Tratándose de activos individuales distintos a garantías personales, se deberá anotar la clave “NA” (No aplica) en este campo. (NR).
 </t>
@@ -253,6 +232,27 @@
   </si>
   <si>
     <t>En miles redondeado sin decimales</t>
+  </si>
+  <si>
+    <t>C_GARANT_ANEXO_A</t>
+  </si>
+  <si>
+    <t>C_CASFIM</t>
+  </si>
+  <si>
+    <t>C_GARANT_ANEXO_AD</t>
+  </si>
+  <si>
+    <t>C_GARANT_ANEXO_AF</t>
+  </si>
+  <si>
+    <t>C_GARANT_ANEXO_E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESCRIPTION </t>
+  </si>
+  <si>
+    <t>COMMENTS</t>
   </si>
 </sst>
 </file>
@@ -387,10 +387,10 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Tipo"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Longitud" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Uso" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Descripcion" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="DESCRIPTION " dataDxfId="3"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Validacion1" dataDxfId="2"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Catalogo" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="Comentario BW" dataDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="COMMENTS" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -660,13 +660,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A3:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="106.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="106.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -674,7 +674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
@@ -682,7 +682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
@@ -690,7 +690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>6</v>
       </c>
@@ -698,7 +698,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>8</v>
       </c>
@@ -723,20 +723,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.6328125" customWidth="1"/>
-    <col min="4" max="4" width="13.26953125" customWidth="1"/>
-    <col min="5" max="5" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="60.453125" customWidth="1"/>
-    <col min="7" max="7" width="35.453125" customWidth="1"/>
-    <col min="8" max="8" width="14.54296875" customWidth="1"/>
-    <col min="9" max="9" width="172.7265625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" customWidth="1"/>
+    <col min="5" max="5" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="60.44140625" customWidth="1"/>
+    <col min="7" max="7" width="20.77734375" customWidth="1"/>
+    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="172.77734375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -753,396 +753,393 @@
         <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="G1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s">
         <v>15</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>+A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" s="4">
         <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" ref="A4:A15" si="0">+A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D7" s="6">
         <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" s="6">
         <v>20</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="6">
         <v>6</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="8"/>
@@ -1158,14 +1155,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf35dce2-b600-471d-a6b0-9e8301b7851b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de82841-ffbb-418b-a888-39c303bacd30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1370,21 +1365,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf35dce2-b600-471d-a6b0-9e8301b7851b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de82841-ffbb-418b-a888-39c303bacd30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDD89CE8-2B1D-4C28-B91D-82C00A34AED7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{035D3778-BC96-4018-ABF2-97634180FD4A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
-    <ds:schemaRef ds:uri="3de82841-ffbb-418b-a888-39c303bacd30"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1409,9 +1403,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{035D3778-BC96-4018-ABF2-97634180FD4A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDD89CE8-2B1D-4C28-B91D-82C00A34AED7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
+    <ds:schemaRef ds:uri="3de82841-ffbb-418b-a888-39c303bacd30"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>